--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -7,8 +7,8 @@
     <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="character_info" sheetId="1" r:id="rId1"/>
+    <sheet name="character_favor_info" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -37,6 +37,9 @@
     <t>key</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -47,6 +50,33 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>smith_wang</t>
+  </si>
+  <si>
+    <t>老铁匠</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>favor_level</t>
+  </si>
+  <si>
+    <t>need_value</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>好感度等级</t>
+  </si>
+  <si>
+    <t>需求好感度</t>
   </si>
 </sst>
 </file>
@@ -978,52 +1008,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
     </row>
@@ -1037,9 +1084,143 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="4" width="9.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="character_info" sheetId="1" r:id="rId1"/>
@@ -1087,7 +1087,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="4" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">

--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -1,250 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="character_info" sheetId="1" r:id="rId1"/>
-    <sheet name="character_favor_info" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="character_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>smith_wang</t>
-  </si>
-  <si>
-    <t>老铁匠</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>favor_level</t>
-  </si>
-  <si>
-    <t>need_value</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>好感度等级</t>
-  </si>
-  <si>
-    <t>需求好感度</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -544,159 +473,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -750,11 +679,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1006,236 +998,317 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col width="14.625" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-    </row>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>老铁匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>镇长</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>木匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col width="25.5" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.375" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>favor_level</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>need_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>好感度等级</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>需求好感度</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9" s="1">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-      <c r="E9">
+      <c r="E9" s="0" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -1,262 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="character_info" sheetId="1" r:id="rId1"/>
-    <sheet name="character_favor_info" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>smith_wang</t>
-  </si>
-  <si>
-    <t>老铁匠</t>
-  </si>
-  <si>
-    <t>home_elder</t>
-  </si>
-  <si>
-    <t>镇长</t>
-  </si>
-  <si>
-    <t>home_merchant</t>
-  </si>
-  <si>
-    <t>木匠</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>favor_level</t>
-  </si>
-  <si>
-    <t>need_value</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>好感度等级</t>
-  </si>
-  <si>
-    <t>需求好感度</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -556,159 +473,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -762,11 +679,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1018,234 +998,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="2" max="2" width="14.625" style="1" customWidth="1"/>
+    <col width="14.625" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>名字</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>老铁匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>镇长</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" s="1">
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>木匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="1">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="25.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" style="1" customWidth="1"/>
+    <col width="25.5" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.375" customWidth="1" style="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>favor_level</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>need_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>好感度等级</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>需求好感度</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9">
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>smith_wang</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
+      <c r="E9" s="0" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="character_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>镇长</t>
+          <t>埃蒙</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>木匠</t>
+          <t>灰露棚看管人</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -2,16 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="character_info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="character_gift_rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,154 +18,112 @@
   <fonts count="20">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color theme="0"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+    </font>
+    <font>
+      <name val="宋体"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -181,198 +136,161 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
@@ -386,25 +304,16 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -419,7 +328,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -434,7 +342,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -449,46 +356,38 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -497,7 +396,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -621,64 +520,66 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -791,76 +692,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -884,9 +725,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -896,27 +735,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -925,7 +760,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -968,17 +802,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -993,7 +827,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1003,121 +836,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.625" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>supports_favor</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>preferred_gift_tags</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>disliked_gift_tags</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>gifts_per_day</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),EGiftTag</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=|),EGiftTag</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>名字</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>是否支持好感度</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>喜欢的礼物类型</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>讨厌的礼物类型</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>每日送礼上限</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>老铁匠</t>
         </is>
       </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>埃蒙</t>
         </is>
       </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" s="1">
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>灰露棚看管人</t>
         </is>
       </c>
+      <c r="D7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" s="1">
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>carlisle</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>卡莱尔</t>
         </is>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Luxury</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1127,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.5" customWidth="1" style="1" min="3" max="3"/>
@@ -1135,176 +1079,281 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>favor_level</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>need_value</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>breakthrough_conds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>好感度等级</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>需求好感度</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>突破条件</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>40</v>
       </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="2" t="n">
         <v>60</v>
       </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <v>80</v>
       </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>smith_wang</t>
         </is>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,1,0,0,0,small_stone,""</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1318,6 +1367,123 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>favor_value</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>receive_dialog_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>规则id</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>角色key</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>物品id</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>固定好感变化值</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>收礼对话id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character_gift_rule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="character_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="character_favor_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="character_gift_rule" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.625" customWidth="1" style="1" min="2" max="2"/>
@@ -1175,6 +1175,42 @@
         <v>0</v>
       </c>
       <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>fei_thief</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>盗贼菲</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>merchant_mei</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>商人梅</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Config/Datas/character.xlsx
+++ b/Config/Datas/character.xlsx
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.625" customWidth="1" style="1" min="2" max="2"/>
@@ -1197,20 +1197,40 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>merchant_mei</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>商人梅</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>药草商人</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
